--- a/data/artefacts.xlsx
+++ b/data/artefacts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://my.shell.com/personal/shatakshi_shree_shell_com/Documents/Desktop/Shell/nuCleus/2026/AI Chatbot/ToolKit - Working - Copy - Copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://my.shell.com/personal/shaunak_goswami_shell_com/Documents/Desktop/nuCleus/2026/ABAP_AI_Assistant_Tool/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_F25DC773A252ABDACC1048F1D1DB573C5BDE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA34AF7D-1972-4F2F-8C0A-F26AB092289F}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_F25DC773A252ABDACC1048F1D1DB573C5BDE5901" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B949B05-FC49-4218-B609-A3DAF6BEF46E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>H94</t>
   </si>
@@ -64,6 +64,18 @@
   </si>
   <si>
     <t>Testing Class</t>
+  </si>
+  <si>
+    <t>ZR_COMPIDOCSEGMENTVRS</t>
+  </si>
+  <si>
+    <t>System_Name</t>
+  </si>
+  <si>
+    <t>nuCleus</t>
+  </si>
+  <si>
+    <t>IDOC Version Comparison</t>
   </si>
 </sst>
 </file>
@@ -130,10 +142,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -399,15 +407,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.08984375" customWidth="1"/>
     <col min="2" max="2" width="35.7265625" customWidth="1"/>
     <col min="3" max="3" width="76.54296875" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -417,8 +426,11 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -428,8 +440,11 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -439,8 +454,11 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -450,8 +468,11 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -460,6 +481,23 @@
       </c>
       <c r="C5" t="s">
         <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
